--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2024_metropolitana.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2024_metropolitana.xlsx
@@ -70,7 +70,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:55</t>
+    <t xml:space="preserve">2026-09-09 21:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2024_metropolitana.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2024_metropolitana.xlsx
@@ -70,7 +70,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 21:02</t>
+    <t xml:space="preserve">2026-09-18 10:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1304,7 +1304,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>3</v>
@@ -1313,12 +1313,12 @@
         <v>30</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>17.95</v>
+        <v>21.11</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>3</v>
@@ -1327,12 +1327,12 @@
         <v>31</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>52.29</v>
+        <v>53.84</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>3</v>
@@ -1341,7 +1341,7 @@
         <v>32</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>87.51</v>
+        <v>85.14</v>
       </c>
     </row>
     <row r="5">
@@ -1388,7 +1388,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>3</v>
@@ -1397,12 +1397,12 @@
         <v>30</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>19.68</v>
+        <v>17.95</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>3</v>
@@ -1411,12 +1411,12 @@
         <v>31</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>56.84</v>
+        <v>52.29</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>3</v>
@@ -1425,12 +1425,12 @@
         <v>32</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>89.34</v>
+        <v>87.51</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>3</v>
@@ -1439,12 +1439,12 @@
         <v>30</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>20.4</v>
+        <v>19.68</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>3</v>
@@ -1453,12 +1453,12 @@
         <v>31</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>54.36</v>
+        <v>56.84</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>3</v>
@@ -1467,12 +1467,12 @@
         <v>32</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>85.42</v>
+        <v>89.34</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>3</v>
@@ -1481,12 +1481,12 @@
         <v>30</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>21.11</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>3</v>
@@ -1495,12 +1495,12 @@
         <v>31</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>53.84</v>
+        <v>54.36</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>3</v>
@@ -1509,7 +1509,7 @@
         <v>32</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>85.14</v>
+        <v>85.42</v>
       </c>
     </row>
     <row r="17">
@@ -1556,7 +1556,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>10</v>
@@ -1565,12 +1565,12 @@
         <v>33</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>93.02</v>
+        <v>92.02</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>10</v>
@@ -1579,7 +1579,7 @@
         <v>34</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>92.45</v>
+        <v>90.82</v>
       </c>
     </row>
     <row r="22">
@@ -1612,7 +1612,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>10</v>
@@ -1621,12 +1621,12 @@
         <v>33</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>93.55</v>
+        <v>93.02</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>10</v>
@@ -1635,12 +1635,12 @@
         <v>34</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>93.83</v>
+        <v>92.45</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>10</v>
@@ -1649,12 +1649,12 @@
         <v>33</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>93.03</v>
+        <v>93.55</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>10</v>
@@ -1663,12 +1663,12 @@
         <v>34</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>94.43</v>
+        <v>93.83</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>10</v>
@@ -1677,12 +1677,12 @@
         <v>33</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>92.02</v>
+        <v>93.03</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>10</v>
@@ -1691,7 +1691,7 @@
         <v>34</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>90.82</v>
+        <v>94.43</v>
       </c>
     </row>
     <row r="30">
@@ -1724,7 +1724,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>11</v>
@@ -1733,12 +1733,12 @@
         <v>35</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>82.46</v>
+        <v>84.65</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>11</v>
@@ -1747,7 +1747,7 @@
         <v>36</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>86.86</v>
+        <v>86.63</v>
       </c>
     </row>
     <row r="34">
@@ -1780,7 +1780,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>11</v>
@@ -1789,12 +1789,12 @@
         <v>35</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>87.03</v>
+        <v>82.46</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>11</v>
@@ -1803,12 +1803,12 @@
         <v>36</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>87.18</v>
+        <v>86.86</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>11</v>
@@ -1817,12 +1817,12 @@
         <v>35</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>88.88</v>
+        <v>87.03</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>11</v>
@@ -1831,12 +1831,12 @@
         <v>36</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>85.7</v>
+        <v>87.18</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>11</v>
@@ -1845,12 +1845,12 @@
         <v>35</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>84.65</v>
+        <v>88.88</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>11</v>
@@ -1859,7 +1859,7 @@
         <v>36</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>86.63</v>
+        <v>85.7</v>
       </c>
     </row>
     <row r="42">

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2024_metropolitana.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2024_metropolitana.xlsx
@@ -70,7 +70,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:52</t>
+    <t xml:space="preserve">2026-09-23 16:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2024_metropolitana.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_provincial_2024_metropolitana.xlsx
@@ -70,7 +70,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 16:35</t>
+    <t xml:space="preserve">2026-10-05 06:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
